--- a/data/trans_dic/IP19C01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por revisión o chequeo</t>
+          <t>Menores que en su última visita al dentista fue por revisión o chequeo (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>57,12; 89,24</t>
+          <t>56,35; 89,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,18; 80,73</t>
+          <t>46,9; 80,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,17; 67,49</t>
+          <t>39,61; 68,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96,18; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,02; 82,57</t>
+          <t>52,19; 82,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,68; 68,82</t>
+          <t>37,86; 67,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,55; 76,04</t>
+          <t>49,06; 77,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91,5; 100,0</t>
+          <t>90,96; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,65; 80,82</t>
+          <t>59,63; 81,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,92; 69,99</t>
+          <t>47,07; 69,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,5; 69,17</t>
+          <t>48,53; 69,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,07; 100,0</t>
+          <t>95,24; 100,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,95; 83,77</t>
+          <t>66,13; 84,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,22; 89,33</t>
+          <t>70,92; 89,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,26; 83,57</t>
+          <t>61,93; 83,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,26; 74,25</t>
+          <t>51,14; 73,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,66; 83,25</t>
+          <t>66,11; 83,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,04; 85,78</t>
+          <t>69,56; 87,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,36; 78,16</t>
+          <t>59,09; 78,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,03; 76,93</t>
+          <t>53,68; 76,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69,22; 81,72</t>
+          <t>69,33; 81,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,23; 85,64</t>
+          <t>73,81; 85,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63,97; 78,86</t>
+          <t>64,58; 78,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,77; 73,5</t>
+          <t>56,65; 73,16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,03; 64,78</t>
+          <t>35,83; 64,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73,09; 93,85</t>
+          <t>73,16; 93,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68,91; 90,96</t>
+          <t>67,98; 92,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,27; 88,88</t>
+          <t>66,55; 89,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,48; 82,46</t>
+          <t>57,91; 82,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,49; 96,65</t>
+          <t>79,89; 95,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,07; 95,49</t>
+          <t>76,29; 95,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72,48; 92,92</t>
+          <t>72,19; 93,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,23; 69,27</t>
+          <t>51,67; 71,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80,43; 93,38</t>
+          <t>80,55; 93,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77,08; 91,81</t>
+          <t>76,44; 91,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>72,99; 88,53</t>
+          <t>74,64; 89,61</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,03; 73,8</t>
+          <t>50,18; 74,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,58; 76,15</t>
+          <t>51,89; 77,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,75; 67,49</t>
+          <t>43,22; 67,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,65; 78,34</t>
+          <t>52,04; 78,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,58; 90,12</t>
+          <t>70,49; 90,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,92; 84,39</t>
+          <t>62,84; 86,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,34; 83,57</t>
+          <t>63,2; 84,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,22; 89,23</t>
+          <t>58,9; 89,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,5; 78,83</t>
+          <t>62,87; 79,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,97; 77,6</t>
+          <t>60,73; 77,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,45; 73,83</t>
+          <t>57,74; 73,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,77; 82,23</t>
+          <t>59,67; 81,25</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,55; 77,98</t>
+          <t>45,26; 79,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,94; 94,62</t>
+          <t>70,33; 94,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55,52; 94,73</t>
+          <t>57,28; 94,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91,54; 100,0</t>
+          <t>92,87; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>53,61; 87,32</t>
+          <t>56,28; 87,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,53; 95,22</t>
+          <t>72,62; 95,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,75; 92,99</t>
+          <t>60,65; 92,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87,84; 100,0</t>
+          <t>89,65; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55,9; 77,94</t>
+          <t>56,5; 78,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78,32; 93,13</t>
+          <t>77,31; 93,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66,32; 90,17</t>
+          <t>65,73; 89,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>92,61; 99,29</t>
+          <t>93,34; 99,29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,79; 72,18</t>
+          <t>40,25; 72,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65,04; 88,53</t>
+          <t>66,0; 89,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,15; 89,44</t>
+          <t>68,84; 89,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,18; 100,0</t>
+          <t>85,0; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,35; 79,21</t>
+          <t>52,49; 79,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,13; 90,55</t>
+          <t>68,19; 91,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70,45; 92,39</t>
+          <t>71,0; 91,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63,68; 89,64</t>
+          <t>63,22; 90,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,9; 72,38</t>
+          <t>51,2; 71,4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71,77; 87,01</t>
+          <t>70,57; 86,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73,67; 88,11</t>
+          <t>74,28; 88,17</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>78,83; 93,72</t>
+          <t>79,75; 93,91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58,48; 77,41</t>
+          <t>58,16; 76,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,28; 81,45</t>
+          <t>61,81; 81,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,6; 92,92</t>
+          <t>78,75; 92,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64,39; 82,06</t>
+          <t>64,45; 81,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,79; 75,92</t>
+          <t>57,86; 75,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,35; 87,6</t>
+          <t>70,53; 87,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,43; 93,23</t>
+          <t>79,95; 93,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68,85; 84,38</t>
+          <t>68,12; 83,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60,53; 73,43</t>
+          <t>60,71; 73,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69,51; 82,01</t>
+          <t>69,96; 82,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81,99; 91,53</t>
+          <t>81,72; 91,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,83; 81,29</t>
+          <t>69,58; 81,11</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>59,31; 75,72</t>
+          <t>58,67; 75,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,7; 66,7</t>
+          <t>48,73; 66,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63,17; 79,22</t>
+          <t>63,08; 78,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89,23; 98,06</t>
+          <t>88,93; 98,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,97; 77,19</t>
+          <t>60,11; 76,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,58; 73,53</t>
+          <t>56,28; 73,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,55; 75,78</t>
+          <t>56,89; 75,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86,96; 96,07</t>
+          <t>86,74; 95,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62,66; 74,02</t>
+          <t>61,98; 74,0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,22; 67,11</t>
+          <t>54,67; 67,3</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62,51; 74,61</t>
+          <t>62,61; 74,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>89,39; 96,26</t>
+          <t>89,9; 96,19</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61,4; 69,76</t>
+          <t>61,94; 69,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>67,86; 75,75</t>
+          <t>68,27; 75,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69,6; 77,51</t>
+          <t>69,4; 77,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77,96; 84,91</t>
+          <t>78,06; 85,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67,59; 75,19</t>
+          <t>67,68; 75,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,97; 79,4</t>
+          <t>72,12; 79,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,68</t>
+          <t>72,03; 79,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>78,51; 85,69</t>
+          <t>78,33; 85,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>65,89; 71,63</t>
+          <t>65,98; 71,78</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71,46; 76,69</t>
+          <t>71,36; 76,73</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72,09; 77,36</t>
+          <t>71,97; 77,37</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>79,73; 84,54</t>
+          <t>79,27; 84,32</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por revisión o chequeo (tasa de respuesta: 99,77%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>14692</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16054</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16313</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34818</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18149</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16861</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20017</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>39191</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>32840</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32914</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>36329</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>74008</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10888; 17249</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11447; 19719</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11983; 20774</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13840; 21893</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11756; 20998</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15340; 24251</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>36261; 39865</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>27332; 37258</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>26106; 38670</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>29855; 42675</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>71128; 74682</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>43577</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>43124</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39503</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44168</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>49148</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45538</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40893</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>48964</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>92725</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>88663</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>80396</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>93132</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>37839; 48348</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37617; 47254</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>33136; 44411</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35209; 50675</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>42952; 54120</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>40087; 50249</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>34724; 45853</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>39633; 56678</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>84721; 99620</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>81689; 95105</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>72507; 87727</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>80818; 104383</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>17136</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28688</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26809</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25263</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25353</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35452</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>28467</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>33995</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>42490</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64140</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>55276</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>59257</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12288; 22150</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24482; 31437</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22107; 30048</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21180; 28352</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>20460; 29066</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31511; 37555</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24506; 30690</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>28912; 37250</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>35970; 49601</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>58725; 68103</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>49411; 59420</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>53647; 64406</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>26268</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27144</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26134</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28487</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>33783</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>30696</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38188</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>44334</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>60051</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>57840</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>64322</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>72822</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>21056; 31460</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>21690; 32567</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20118; 31232</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22298; 33828</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>29354; 37515</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>25908; 35487</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>32232; 43046</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>34553; 52537</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>52559; 66675</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>50424; 64405</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>56328; 71955</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>60562; 82467</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>16774</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22316</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11959</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>24863</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24217</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13818</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>33452</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>32980</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>46532</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>25776</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>58315</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>11855; 20757</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18334; 24682</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8617; 14279</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23488; 25292</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12644; 19673</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20065; 26290</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10352; 15838</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>31044; 34627</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>27490; 37970</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>41511; 50168</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>21107; 28826</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>55929; 59492</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>14282</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>27876</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31958</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>25823</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>18770</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>27010</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>33712</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>21436</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>33051</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>54886</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>65670</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>47260</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>10200; 18266</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>23380; 31629</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>27357; 35567</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>22917; 26962</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>14885; 22645</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>22610; 30364</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>28805; 36934</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>17033; 24377</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>27494; 38342</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>48400; 59467</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>59656; 70815</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>42992; 50625</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>44326</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>46608</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>58627</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>57459</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45419</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>53746</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>54247</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>83716</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>89746</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>100354</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>112874</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>141175</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>37970; 50098</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>39539; 52104</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>53111; 62452</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>50117; 63294</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>39359; 51549</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>47368; 58506</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>49522; 57914</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>74036; 91178</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>80934; 97547</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>91741; 108624</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>105735; 118367</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>129732; 151232</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>55162</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>44983</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>57265</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>78985</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>51392</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>45612</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>52633</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>94184</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>106555</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>90594</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>109898</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>173168</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>47713; 61536</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>37932; 51713</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>50452; 62930</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>74078; 81628</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>44727; 56960</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>39447; 51251</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>44747; 59025</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>88280; 97634</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>96526; 115249</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>80873; 99563</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>99321; 118704</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>166387; 178026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>232218</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>256792</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>268568</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>319866</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>399272</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>490437</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>535924</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>550541</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>719137</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>217367; 245325</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>243057; 269024</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>253328; 282120</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>305727; 332886</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>244823; 271292</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>264985; 292453</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>267518; 294469</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>379470; 414420</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>470225; 511548</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>516222; 555101</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>529969; 569772</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>694445; 738683</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Provincia-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56,35; 89,28</t>
+          <t>59,62; 89,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,9; 80,8</t>
+          <t>48,28; 80,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,61; 68,68</t>
+          <t>39,75; 69,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,19; 82,56</t>
+          <t>51,71; 82,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,86; 67,62</t>
+          <t>37,97; 68,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,06; 77,56</t>
+          <t>48,79; 76,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,96; 100,0</t>
+          <t>92,89; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,63; 81,28</t>
+          <t>59,61; 82,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,07; 69,73</t>
+          <t>48,4; 69,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48,53; 69,37</t>
+          <t>47,82; 68,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,24; 100,0</t>
+          <t>94,8; 100,0</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,13; 84,49</t>
+          <t>67,6; 84,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,92; 89,08</t>
+          <t>70,1; 88,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,93; 83,0</t>
+          <t>61,75; 82,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,14; 73,61</t>
+          <t>51,68; 74,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,11; 83,29</t>
+          <t>66,82; 83,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,56; 87,19</t>
+          <t>70,23; 86,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,09; 78,02</t>
+          <t>58,74; 78,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,68; 76,77</t>
+          <t>54,64; 76,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69,33; 81,52</t>
+          <t>69,32; 81,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,81; 85,93</t>
+          <t>73,18; 85,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,58; 78,13</t>
+          <t>63,67; 77,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,65; 73,16</t>
+          <t>57,41; 73,62</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,83; 64,59</t>
+          <t>35,64; 64,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73,16; 93,95</t>
+          <t>73,1; 93,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,98; 92,41</t>
+          <t>69,44; 92,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66,55; 89,09</t>
+          <t>65,17; 88,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,91; 82,27</t>
+          <t>59,31; 82,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,89; 95,21</t>
+          <t>81,24; 96,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,29; 95,54</t>
+          <t>75,18; 95,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72,19; 93,0</t>
+          <t>73,92; 93,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,67; 71,24</t>
+          <t>51,77; 70,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80,55; 93,41</t>
+          <t>80,7; 93,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76,44; 91,92</t>
+          <t>76,13; 92,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,64; 89,61</t>
+          <t>74,39; 89,12</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,18; 74,98</t>
+          <t>50,21; 74,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,89; 77,92</t>
+          <t>53,13; 76,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,22; 67,1</t>
+          <t>43,13; 67,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,04; 78,96</t>
+          <t>52,74; 79,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,49; 90,09</t>
+          <t>70,27; 90,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,84; 86,08</t>
+          <t>60,84; 84,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,2; 84,4</t>
+          <t>62,15; 84,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,9; 89,56</t>
+          <t>58,24; 89,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,87; 79,76</t>
+          <t>62,88; 79,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,73; 77,57</t>
+          <t>59,5; 77,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,74; 73,76</t>
+          <t>57,33; 74,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,67; 81,25</t>
+          <t>61,27; 82,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,26; 79,25</t>
+          <t>47,06; 78,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,33; 94,68</t>
+          <t>67,92; 94,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,28; 94,92</t>
+          <t>53,92; 93,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92,87; 100,0</t>
+          <t>91,31; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,28; 87,56</t>
+          <t>56,78; 87,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,62; 95,15</t>
+          <t>75,57; 95,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,65; 92,79</t>
+          <t>60,98; 92,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>89,65; 100,0</t>
+          <t>88,78; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56,5; 78,03</t>
+          <t>56,25; 77,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77,31; 93,43</t>
+          <t>77,45; 93,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,73; 89,77</t>
+          <t>67,9; 90,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,34; 99,29</t>
+          <t>92,79; 99,29</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,25; 72,08</t>
+          <t>39,86; 71,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,0; 89,28</t>
+          <t>66,43; 88,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,84; 89,49</t>
+          <t>69,55; 89,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,0; 100,0</t>
+          <t>85,64; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,49; 79,85</t>
+          <t>50,57; 79,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,19; 91,57</t>
+          <t>67,39; 91,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,0; 91,04</t>
+          <t>71,42; 90,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63,22; 90,47</t>
+          <t>64,86; 89,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51,2; 71,4</t>
+          <t>50,77; 72,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70,57; 86,71</t>
+          <t>70,37; 86,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>74,28; 88,17</t>
+          <t>73,75; 88,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79,75; 93,91</t>
+          <t>79,61; 93,15</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58,16; 76,74</t>
+          <t>58,42; 77,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61,81; 81,45</t>
+          <t>62,56; 81,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,75; 92,6</t>
+          <t>78,95; 92,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64,45; 81,4</t>
+          <t>64,61; 81,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,86; 75,78</t>
+          <t>56,8; 74,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,53; 87,11</t>
+          <t>70,96; 87,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,95; 93,5</t>
+          <t>78,94; 93,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68,12; 83,89</t>
+          <t>68,26; 84,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60,71; 73,17</t>
+          <t>60,18; 73,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69,96; 82,84</t>
+          <t>69,89; 82,16</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81,72; 91,48</t>
+          <t>81,67; 91,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,58; 81,11</t>
+          <t>69,01; 80,96</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>58,67; 75,67</t>
+          <t>60,18; 76,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,73; 66,43</t>
+          <t>48,79; 66,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63,08; 78,69</t>
+          <t>63,64; 79,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88,93; 98,0</t>
+          <t>88,42; 98,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,11; 76,55</t>
+          <t>60,31; 76,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,28; 73,13</t>
+          <t>55,72; 74,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,89; 75,04</t>
+          <t>58,1; 74,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86,74; 95,93</t>
+          <t>86,96; 96,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61,98; 74,0</t>
+          <t>62,81; 73,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,67; 67,3</t>
+          <t>54,42; 66,63</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62,61; 74,83</t>
+          <t>63,44; 74,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>89,9; 96,19</t>
+          <t>89,63; 96,38</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61,94; 69,91</t>
+          <t>61,72; 69,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68,27; 75,56</t>
+          <t>68,27; 76,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69,4; 77,29</t>
+          <t>69,72; 77,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78,06; 85,0</t>
+          <t>77,71; 84,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67,68; 75,0</t>
+          <t>67,62; 74,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>72,12; 79,6</t>
+          <t>72,1; 79,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,03; 79,29</t>
+          <t>72,19; 79,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>78,33; 85,55</t>
+          <t>78,68; 85,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>65,98; 71,78</t>
+          <t>66,07; 71,47</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71,36; 76,73</t>
+          <t>71,43; 76,57</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71,97; 77,37</t>
+          <t>72,01; 77,22</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>79,27; 84,32</t>
+          <t>79,53; 84,44</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10888; 17249</t>
+          <t>11519; 17259</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11447; 19719</t>
+          <t>11782; 19571</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11983; 20774</t>
+          <t>12023; 20901</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,42 +2229,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13840; 21893</t>
+          <t>13714; 21841</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11756; 20998</t>
+          <t>11790; 21405</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15340; 24251</t>
+          <t>15256; 24025</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36261; 39865</t>
+          <t>37031; 39865</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27332; 37258</t>
+          <t>27327; 37740</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26106; 38670</t>
+          <t>26841; 38807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29855; 42675</t>
+          <t>29417; 42371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71128; 74682</t>
+          <t>70798; 74682</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37839; 48348</t>
+          <t>38680; 48531</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37617; 47254</t>
+          <t>37183; 47200</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33136; 44411</t>
+          <t>33040; 44028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35209; 50675</t>
+          <t>35577; 51447</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42952; 54120</t>
+          <t>43415; 54160</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40087; 50249</t>
+          <t>40472; 50042</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34724; 45853</t>
+          <t>34523; 46047</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39633; 56678</t>
+          <t>40339; 56582</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>84721; 99620</t>
+          <t>84702; 100078</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81689; 95105</t>
+          <t>80992; 94637</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72507; 87727</t>
+          <t>71487; 87423</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80818; 104383</t>
+          <t>81909; 105032</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12288; 22150</t>
+          <t>12220; 22167</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24482; 31437</t>
+          <t>24460; 31437</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22107; 30048</t>
+          <t>22579; 30211</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21180; 28352</t>
+          <t>20739; 28303</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20460; 29066</t>
+          <t>20954; 29111</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31511; 37555</t>
+          <t>32043; 38100</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24506; 30690</t>
+          <t>24152; 30745</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28912; 37250</t>
+          <t>29608; 37350</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35970; 49601</t>
+          <t>36045; 48940</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58725; 68103</t>
+          <t>58839; 68091</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49411; 59420</t>
+          <t>49208; 59538</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53647; 64406</t>
+          <t>53470; 64053</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21056; 31460</t>
+          <t>21066; 31353</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21690; 32567</t>
+          <t>22205; 32175</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20118; 31232</t>
+          <t>20075; 31216</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22298; 33828</t>
+          <t>22596; 34216</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29354; 37515</t>
+          <t>29262; 37547</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25908; 35487</t>
+          <t>25082; 34999</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32232; 43046</t>
+          <t>31701; 43022</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34553; 52537</t>
+          <t>34163; 52508</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52559; 66675</t>
+          <t>52571; 66288</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50424; 64405</t>
+          <t>49401; 64087</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56328; 71955</t>
+          <t>55929; 72223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>60562; 82467</t>
+          <t>62196; 83606</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11855; 20757</t>
+          <t>12326; 20449</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18334; 24682</t>
+          <t>17705; 24637</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8617; 14279</t>
+          <t>8112; 14008</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23488; 25292</t>
+          <t>23095; 25292</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12644; 19673</t>
+          <t>12757; 19674</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20065; 26290</t>
+          <t>20879; 26317</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10352; 15838</t>
+          <t>10409; 15864</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>31044; 34627</t>
+          <t>30744; 34627</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27490; 37970</t>
+          <t>27370; 37512</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41511; 50168</t>
+          <t>41589; 50036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21107; 28826</t>
+          <t>21802; 29146</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55929; 59492</t>
+          <t>55597; 59495</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10200; 18266</t>
+          <t>10101; 18060</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23380; 31629</t>
+          <t>23533; 31510</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27357; 35567</t>
+          <t>27643; 35422</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22917; 26962</t>
+          <t>23091; 26962</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14885; 22645</t>
+          <t>14340; 22610</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22610; 30364</t>
+          <t>22345; 30216</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28805; 36934</t>
+          <t>28974; 36859</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17033; 24377</t>
+          <t>17477; 24177</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27494; 38342</t>
+          <t>27264; 39084</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48400; 59467</t>
+          <t>48262; 59461</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59656; 70815</t>
+          <t>59228; 70851</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42992; 50625</t>
+          <t>42918; 50214</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37970; 50098</t>
+          <t>38140; 50523</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39539; 52104</t>
+          <t>40018; 52132</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53111; 62452</t>
+          <t>53244; 62271</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50117; 63294</t>
+          <t>50235; 63579</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39359; 51549</t>
+          <t>38642; 50880</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47368; 58506</t>
+          <t>47658; 58458</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49522; 57914</t>
+          <t>48895; 57860</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>74036; 91178</t>
+          <t>74189; 91532</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>80934; 97547</t>
+          <t>80231; 97608</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>91741; 108624</t>
+          <t>91655; 107733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105735; 118367</t>
+          <t>105667; 117992</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>129732; 151232</t>
+          <t>128658; 150945</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>47713; 61536</t>
+          <t>48942; 62239</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37932; 51713</t>
+          <t>37985; 51518</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>50452; 62930</t>
+          <t>50897; 63465</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>74078; 81628</t>
+          <t>73647; 81706</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44727; 56960</t>
+          <t>44876; 57266</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39447; 51251</t>
+          <t>39052; 52257</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44747; 59025</t>
+          <t>45700; 58657</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>88280; 97634</t>
+          <t>88502; 97930</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>96526; 115249</t>
+          <t>97811; 115091</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>80873; 99563</t>
+          <t>80504; 98574</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99321; 118704</t>
+          <t>100634; 118846</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>166387; 178026</t>
+          <t>165876; 178379</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>217367; 245325</t>
+          <t>216587; 244928</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>243057; 269024</t>
+          <t>243040; 270963</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>253328; 282120</t>
+          <t>254511; 283010</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>305727; 332886</t>
+          <t>304341; 332207</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>244823; 271292</t>
+          <t>244598; 271064</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>264985; 292453</t>
+          <t>264906; 292529</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>267518; 294469</t>
+          <t>268115; 294193</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>379470; 414420</t>
+          <t>381145; 414784</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>470225; 511548</t>
+          <t>470844; 509320</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>516222; 555101</t>
+          <t>516752; 553917</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>529969; 569772</t>
+          <t>530285; 568634</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>694445; 738683</t>
+          <t>696742; 739765</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>68,44%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54,3%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64,02%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>76,04%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>65,78%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>53,93%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>68,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>71,64%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,62; 89,33</t>
+          <t>52,02; 82,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,28; 80,19</t>
+          <t>38,68; 68,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,75; 69,1</t>
+          <t>48,55; 76,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>91,28; 100,0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>57,12; 89,24</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,18; 80,73</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,17; 67,49</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>51,71; 82,36</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,97; 68,93</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,79; 76,83</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92,89; 100,0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,61; 82,33</t>
+          <t>59,65; 80,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,4; 69,97</t>
+          <t>48,92; 69,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,82; 68,88</t>
+          <t>49,5; 69,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,8; 100,0</t>
+          <t>94,47; 100,0</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75,64%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>79,02%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>69,58%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>66,58%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>76,15%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>81,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>73,83%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>64,16%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>75,64%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>79,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>69,58%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>66,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,6; 84,81</t>
+          <t>66,66; 83,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,1; 88,98</t>
+          <t>70,04; 85,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,75; 82,28</t>
+          <t>59,36; 78,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,68; 74,73</t>
+          <t>54,02; 77,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,82; 83,35</t>
+          <t>65,95; 83,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,23; 86,83</t>
+          <t>71,22; 89,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,74; 78,35</t>
+          <t>62,26; 83,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,64; 76,64</t>
+          <t>55,38; 76,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69,32; 81,9</t>
+          <t>69,22; 81,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,18; 85,51</t>
+          <t>73,23; 85,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63,67; 77,86</t>
+          <t>63,97; 78,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,41; 73,62</t>
+          <t>59,29; 74,39</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71,76%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>89,88%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88,62%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85,53%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>49,97%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>85,73%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>82,45%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>79,38%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,62%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,64; 64,64</t>
+          <t>59,48; 82,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73,1; 93,94</t>
+          <t>79,49; 96,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,44; 92,91</t>
+          <t>75,07; 95,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65,17; 88,94</t>
+          <t>73,55; 93,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,31; 82,4</t>
+          <t>35,03; 64,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,24; 96,59</t>
+          <t>73,09; 93,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,18; 95,71</t>
+          <t>68,91; 90,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73,92; 93,25</t>
+          <t>67,47; 88,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,77; 70,29</t>
+          <t>50,23; 69,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80,7; 93,39</t>
+          <t>80,43; 93,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76,13; 92,11</t>
+          <t>77,08; 91,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,39; 89,12</t>
+          <t>73,09; 88,65</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81,13%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>74,46%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74,87%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73,68%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>62,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>64,94%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>56,15%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>81,13%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>74,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74,87%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,21; 74,72</t>
+          <t>69,58; 90,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,13; 76,98</t>
+          <t>61,92; 84,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,13; 67,07</t>
+          <t>62,34; 83,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,74; 79,86</t>
+          <t>56,41; 87,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,27; 90,17</t>
+          <t>50,03; 73,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,84; 84,89</t>
+          <t>52,58; 76,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,15; 84,35</t>
+          <t>44,75; 67,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,24; 89,51</t>
+          <t>51,0; 77,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,88; 79,29</t>
+          <t>62,5; 78,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,5; 77,19</t>
+          <t>60,97; 77,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,33; 74,04</t>
+          <t>57,45; 73,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,27; 82,37</t>
+          <t>58,78; 80,63</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>72,13%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87,65%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>80,96%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>64,05%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>85,61%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>79,49%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>72,13%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>87,65%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>80,96%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,06; 78,08</t>
+          <t>53,61; 87,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,92; 94,51</t>
+          <t>74,53; 95,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,92; 93,11</t>
+          <t>60,75; 92,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91,31; 100,0</t>
+          <t>87,96; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,78; 87,57</t>
+          <t>46,55; 77,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,57; 95,25</t>
+          <t>69,94; 94,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,98; 92,95</t>
+          <t>55,52; 94,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,78; 100,0</t>
+          <t>91,1; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56,25; 77,09</t>
+          <t>55,9; 77,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77,45; 93,18</t>
+          <t>78,32; 93,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67,9; 90,77</t>
+          <t>66,32; 90,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>92,79; 99,29</t>
+          <t>92,99; 99,23</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>66,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81,46%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>83,1%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>80,42%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>56,36%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>78,69%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>80,41%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>95,78%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>66,19%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,1%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,86; 71,27</t>
+          <t>52,35; 79,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,43; 88,94</t>
+          <t>68,13; 90,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,55; 89,13</t>
+          <t>70,45; 92,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,64; 100,0</t>
+          <t>64,46; 89,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,57; 79,73</t>
+          <t>41,79; 72,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,39; 91,13</t>
+          <t>65,04; 88,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,42; 90,85</t>
+          <t>68,15; 89,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64,86; 89,73</t>
+          <t>84,33; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,77; 72,78</t>
+          <t>50,9; 72,38</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70,37; 86,7</t>
+          <t>71,77; 87,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73,75; 88,22</t>
+          <t>73,67; 88,11</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79,61; 93,15</t>
+          <t>80,37; 94,34</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>66,76%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>80,02%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>87,58%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77,12%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>67,9%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>72,86%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>86,93%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>73,9%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>66,76%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>80,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>87,58%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58,42; 77,39</t>
+          <t>57,79; 75,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,56; 81,49</t>
+          <t>71,35; 87,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,95; 92,33</t>
+          <t>79,43; 93,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64,61; 81,77</t>
+          <t>69,19; 84,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,8; 74,79</t>
+          <t>58,48; 77,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,96; 87,04</t>
+          <t>64,28; 81,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,94; 93,41</t>
+          <t>78,6; 92,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68,26; 84,22</t>
+          <t>62,61; 80,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60,18; 73,22</t>
+          <t>60,53; 73,43</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69,89; 82,16</t>
+          <t>69,51; 82,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81,67; 91,19</t>
+          <t>81,99; 91,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,01; 80,96</t>
+          <t>68,46; 80,55</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>69,06%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>65,08%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>66,91%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>67,83%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>57,78%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>71,6%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>94,83%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>69,06%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>65,08%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>66,91%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>60,18; 76,54</t>
+          <t>60,97; 77,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,79; 66,18</t>
+          <t>55,58; 73,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63,64; 79,36</t>
+          <t>58,55; 75,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88,42; 98,09</t>
+          <t>87,05; 96,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,31; 76,96</t>
+          <t>59,31; 75,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,72; 74,56</t>
+          <t>48,7; 66,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,1; 74,57</t>
+          <t>63,17; 79,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86,96; 96,22</t>
+          <t>89,86; 98,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62,81; 73,9</t>
+          <t>62,66; 74,02</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,42; 66,63</t>
+          <t>54,22; 67,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63,44; 74,92</t>
+          <t>62,51; 74,61</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>89,63; 96,38</t>
+          <t>89,81; 96,45</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>71,38%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>75,98%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>75,92%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>66,17%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>72,13%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>73,58%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>75,98%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>75,92%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61,72; 69,79</t>
+          <t>67,59; 75,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68,27; 76,11</t>
+          <t>71,97; 79,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69,72; 77,53</t>
+          <t>72,19; 79,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77,71; 84,83</t>
+          <t>78,56; 85,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67,62; 74,94</t>
+          <t>61,4; 69,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>72,1; 79,62</t>
+          <t>67,86; 75,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,21</t>
+          <t>69,6; 77,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>78,68; 85,62</t>
+          <t>78,44; 85,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66,07; 71,47</t>
+          <t>65,89; 71,63</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71,43; 76,57</t>
+          <t>71,46; 76,69</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72,01; 77,22</t>
+          <t>72,09; 77,36</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>79,53; 84,44</t>
+          <t>79,84; 84,58</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18149</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16861</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20017</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32709</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>14692</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>16054</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>16313</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34818</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18149</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16861</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20017</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>29492</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74008</t>
+          <t>62201</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11519; 17259</t>
+          <t>13794; 21895</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11782; 19571</t>
+          <t>12012; 21371</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12023; 20901</t>
+          <t>15179; 23778</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>30405; 33310</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11036; 17242</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12246; 19703</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12149; 20415</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13714; 21841</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11790; 21405</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15256; 24025</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>37031; 39865</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27327; 37740</t>
+          <t>27344; 37046</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26841; 38807</t>
+          <t>27130; 38816</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29417; 42371</t>
+          <t>30450; 42549</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70798; 74682</t>
+          <t>59329; 62802</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49148</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45538</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>40893</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>46087</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>43577</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>43124</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>39503</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>44168</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>49148</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45538</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>40893</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>48964</t>
+          <t>45016</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93132</t>
+          <t>91102</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38680; 48531</t>
+          <t>43311; 54089</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37183; 47200</t>
+          <t>40368; 49437</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33040; 44028</t>
+          <t>34886; 45931</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35577; 51447</t>
+          <t>37390; 53903</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43415; 54160</t>
+          <t>37738; 47936</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40472; 50042</t>
+          <t>37778; 47385</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34523; 46047</t>
+          <t>33314; 44718</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40339; 56582</t>
+          <t>37670; 51991</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>84702; 100078</t>
+          <t>84590; 99860</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80992; 94637</t>
+          <t>81048; 94783</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71487; 87423</t>
+          <t>71819; 88538</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81909; 105032</t>
+          <t>81372; 102092</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25353</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35452</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28467</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30328</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>17136</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>28688</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>26809</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25263</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25353</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35452</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>28467</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33995</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59257</t>
+          <t>55354</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12220; 22167</t>
+          <t>21015; 29133</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24460; 31437</t>
+          <t>31355; 38125</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22579; 30211</t>
+          <t>24115; 30676</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20739; 28303</t>
+          <t>26078; 33103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20954; 29111</t>
+          <t>12012; 22213</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32043; 38100</t>
+          <t>24457; 31405</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24152; 30745</t>
+          <t>22407; 29579</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29608; 37350</t>
+          <t>21302; 28082</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36045; 48940</t>
+          <t>34973; 48228</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58839; 68091</t>
+          <t>58642; 68080</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49208; 59538</t>
+          <t>49822; 59346</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53470; 64053</t>
+          <t>48992; 59421</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33783</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30696</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38188</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39922</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>26268</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>27144</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>26134</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28487</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>33783</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30696</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38188</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>44334</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72822</t>
+          <t>70007</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21066; 31353</t>
+          <t>28974; 37528</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22205; 32175</t>
+          <t>25527; 34792</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20075; 31216</t>
+          <t>31796; 42625</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22596; 34216</t>
+          <t>30567; 47394</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29262; 37547</t>
+          <t>20992; 30964</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25082; 34999</t>
+          <t>21976; 31830</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31701; 43022</t>
+          <t>20827; 31414</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34163; 52508</t>
+          <t>23122; 35287</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52571; 66288</t>
+          <t>52253; 65904</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49401; 64087</t>
+          <t>50623; 64423</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55929; 72223</t>
+          <t>56040; 72018</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62196; 83606</t>
+          <t>58497; 80244</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24217</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13818</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>16774</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>22316</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>11959</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24863</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>16205</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24217</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13818</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>26017</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58315</t>
+          <t>58489</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12326; 20449</t>
+          <t>12044; 19618</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17705; 24637</t>
+          <t>20591; 26310</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8112; 14008</t>
+          <t>10369; 15872</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23095; 25292</t>
+          <t>29502; 33539</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12757; 19674</t>
+          <t>12193; 20425</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20879; 26317</t>
+          <t>18233; 24667</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10409; 15864</t>
+          <t>8352; 14252</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30744; 34627</t>
+          <t>24136; 26495</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27370; 37512</t>
+          <t>27201; 37926</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41589; 50036</t>
+          <t>42057; 50011</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21802; 29146</t>
+          <t>21295; 28954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55597; 59495</t>
+          <t>55828; 59569</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18770</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>27010</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>33712</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19576</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>14282</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>27876</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>31958</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>25823</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>18770</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>27010</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>33712</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>47260</t>
+          <t>46215</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10101; 18060</t>
+          <t>14847; 22462</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23533; 31510</t>
+          <t>22592; 30025</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27643; 35422</t>
+          <t>28580; 37484</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23091; 26962</t>
+          <t>15691; 21884</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14340; 22610</t>
+          <t>10589; 18291</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22345; 30216</t>
+          <t>23042; 31362</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28974; 36859</t>
+          <t>27084; 35547</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17477; 24177</t>
+          <t>23448; 27805</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27264; 39084</t>
+          <t>27332; 38865</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48262; 59461</t>
+          <t>49226; 59674</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59228; 70851</t>
+          <t>59170; 70765</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42918; 50214</t>
+          <t>41913; 49194</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>76</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>45419</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>53746</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>54247</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>79156</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>44326</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>46608</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>58627</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>57459</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>45419</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>53746</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>54247</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>83716</t>
+          <t>55053</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>141175</t>
+          <t>134208</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>38140; 50523</t>
+          <t>39315; 51646</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40018; 52132</t>
+          <t>47923; 58835</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53244; 62271</t>
+          <t>49202; 57752</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50235; 63579</t>
+          <t>71023; 86865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38642; 50880</t>
+          <t>38179; 50535</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47658; 58458</t>
+          <t>41122; 52104</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48895; 57860</t>
+          <t>53011; 62671</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>74189; 91532</t>
+          <t>47613; 61307</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>80231; 97608</t>
+          <t>80694; 97886</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>91655; 107733</t>
+          <t>91152; 107543</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105667; 117992</t>
+          <t>106085; 118423</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>128658; 150945</t>
+          <t>122344; 143932</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>106</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>51392</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>45612</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>52633</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>100408</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>55162</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>44983</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>57265</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>78985</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>51392</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>45612</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>52633</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>94184</t>
+          <t>87082</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>173168</t>
+          <t>187490</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>48942; 62239</t>
+          <t>45368; 57442</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37985; 51518</t>
+          <t>38955; 51534</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>50897; 63465</t>
+          <t>46051; 59609</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>73647; 81706</t>
+          <t>94362; 104273</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44876; 57266</t>
+          <t>48228; 61575</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39052; 52257</t>
+          <t>37912; 51926</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>45700; 58657</t>
+          <t>50518; 63359</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>88502; 97930</t>
+          <t>82227; 89806</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>97811; 115091</t>
+          <t>97577; 115270</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>80504; 98574</t>
+          <t>80210; 99279</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>100634; 118846</t>
+          <t>99155; 118362</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>165876; 178379</t>
+          <t>179528; 192805</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>363</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>386</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>460</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>380658</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>232218</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>256792</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>268568</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>319866</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>258220</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>279132</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>281974</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>399272</t>
+          <t>324410</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>719137</t>
+          <t>705067</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>216587; 244928</t>
+          <t>244477; 272001</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>243040; 270963</t>
+          <t>264423; 291726</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>254511; 283010</t>
+          <t>268126; 295931</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>304341; 332207</t>
+          <t>362215; 394644</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>244598; 271064</t>
+          <t>215484; 244818</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>264906; 292529</t>
+          <t>241589; 269703</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>268115; 294193</t>
+          <t>254062; 282940</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>381145; 414784</t>
+          <t>310839; 337298</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>470844; 509320</t>
+          <t>469582; 510472</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>516752; 553917</t>
+          <t>516958; 554768</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>530285; 568634</t>
+          <t>530895; 569710</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>696742; 739765</t>
+          <t>684521; 725196</t>
         </is>
       </c>
     </row>
